--- a/Tabelas Censo 25-02-2025.xlsx
+++ b/Tabelas Censo 25-02-2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar_macieira\Desktop\Usiminas\Nescon\censo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NESCON\Trabalho - Censo\censo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677005AC-FA56-4F24-9FAA-F5A243BA0A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341C4BCD-D51A-4CCB-B0FE-9144B7488013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="11111" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -620,7 +620,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -630,6 +630,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -763,7 +769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -896,46 +902,139 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1235,527 +1334,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:FH62"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.09765625" customWidth="1"/>
-    <col min="3" max="3" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="4" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.8984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.19921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.8984375" style="37" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="26.69921875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.59765625" customWidth="1"/>
-    <col min="33" max="33" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.85546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.5703125" customWidth="1"/>
+    <col min="33" max="33" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="5" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="6" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="5" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="4" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="4" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="4" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="4" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="6" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="56" max="56" width="6" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="5" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="5" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="5" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="4" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="4" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="4" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="73" max="73" width="6" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="16.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="15.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="33.19921875" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="16.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="15.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="64.09765625" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="15.69921875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="16.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="15.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="16.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="15.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="64.140625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="88" max="88" width="33" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="42.19921875" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="34.8984375" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="16.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="15.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="73.296875" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="16.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="15.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="47.796875" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="39.69921875" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="52.69921875" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="18.8984375" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="46.796875" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="122" max="122" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="5.59765625" customWidth="1"/>
-    <col min="128" max="128" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="16.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="15.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="6.59765625" style="2" customWidth="1"/>
+    <col min="89" max="89" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="15.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="73.28515625" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="15.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="5.5703125" customWidth="1"/>
+    <col min="128" max="128" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="15.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="6.5703125" style="2" customWidth="1"/>
     <col min="132" max="132" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="133" max="134" width="15.69921875" style="2" customWidth="1"/>
+    <col min="133" max="134" width="15.7109375" style="2" customWidth="1"/>
     <col min="136" max="136" width="12" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="138" max="138" width="7.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="140" max="140" width="7.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="7.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="7.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="146" max="146" width="7.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="147" max="147" width="7.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="148" max="148" width="6" style="3" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="11.19921875" style="4"/>
+    <col min="137" max="137" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="147" max="147" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="11.140625" style="4"/>
     <col min="151" max="151" width="12" bestFit="1" customWidth="1"/>
     <col min="152" max="152" width="5" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="154" max="154" width="5" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="156" max="156" width="6" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="158" max="158" width="6" bestFit="1" customWidth="1"/>
-    <col min="159" max="159" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="159" max="159" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="160" max="160" width="5" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="163" max="163" width="6" bestFit="1" customWidth="1"/>
-    <col min="164" max="164" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="164" max="164" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:164" x14ac:dyDescent="0.3">
-      <c r="B1" s="50" t="s">
+    <row r="1" spans="2:164" x14ac:dyDescent="0.25">
+      <c r="B1" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
       <c r="V1" s="4"/>
-      <c r="X1" s="50" t="s">
+      <c r="X1" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AB1" s="50" t="s">
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AB1" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AF1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
-      <c r="AM1" s="50"/>
-      <c r="AN1" s="50"/>
-      <c r="AO1" s="50"/>
-      <c r="AP1" s="50"/>
-      <c r="AQ1" s="50"/>
-      <c r="AR1" s="50"/>
-      <c r="AS1" s="50"/>
-      <c r="AT1" s="50"/>
-      <c r="AU1" s="50"/>
-      <c r="AV1" s="50"/>
-      <c r="AW1" s="50"/>
-      <c r="AX1" s="50"/>
-      <c r="AY1" s="50"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
+      <c r="AM1" s="49"/>
+      <c r="AN1" s="49"/>
+      <c r="AO1" s="49"/>
+      <c r="AP1" s="49"/>
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="49"/>
+      <c r="AU1" s="49"/>
+      <c r="AV1" s="49"/>
+      <c r="AW1" s="49"/>
+      <c r="AX1" s="49"/>
+      <c r="AY1" s="49"/>
       <c r="AZ1" s="3"/>
-      <c r="BB1" s="50" t="s">
+      <c r="BB1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="BC1" s="50"/>
-      <c r="BD1" s="50"/>
-      <c r="BE1" s="50"/>
-      <c r="BF1" s="50"/>
-      <c r="BG1" s="50"/>
-      <c r="BH1" s="50"/>
-      <c r="BI1" s="50"/>
-      <c r="BJ1" s="50"/>
-      <c r="BK1" s="50"/>
-      <c r="BL1" s="50"/>
-      <c r="BM1" s="50"/>
-      <c r="BN1" s="50"/>
-      <c r="BO1" s="50"/>
-      <c r="BP1" s="50"/>
-      <c r="BQ1" s="50"/>
-      <c r="BR1" s="50"/>
-      <c r="BS1" s="50"/>
-      <c r="BT1" s="50"/>
-      <c r="BU1" s="50"/>
+      <c r="BC1" s="49"/>
+      <c r="BD1" s="49"/>
+      <c r="BE1" s="49"/>
+      <c r="BF1" s="49"/>
+      <c r="BG1" s="49"/>
+      <c r="BH1" s="49"/>
+      <c r="BI1" s="49"/>
+      <c r="BJ1" s="49"/>
+      <c r="BK1" s="49"/>
+      <c r="BL1" s="49"/>
+      <c r="BM1" s="49"/>
+      <c r="BN1" s="49"/>
+      <c r="BO1" s="49"/>
+      <c r="BP1" s="49"/>
+      <c r="BQ1" s="49"/>
+      <c r="BR1" s="49"/>
+      <c r="BS1" s="49"/>
+      <c r="BT1" s="49"/>
+      <c r="BU1" s="49"/>
       <c r="BV1" s="3"/>
-      <c r="BX1" s="50" t="s">
+      <c r="BX1" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="BY1" s="50"/>
-      <c r="BZ1" s="50"/>
-      <c r="CB1" s="50" t="s">
+      <c r="BY1" s="49"/>
+      <c r="BZ1" s="49"/>
+      <c r="CB1" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="CC1" s="50"/>
-      <c r="CD1" s="50"/>
-      <c r="CF1" s="50" t="s">
+      <c r="CC1" s="49"/>
+      <c r="CD1" s="49"/>
+      <c r="CF1" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="CG1" s="50"/>
-      <c r="CH1" s="50"/>
-      <c r="CJ1" s="50" t="s">
+      <c r="CG1" s="49"/>
+      <c r="CH1" s="49"/>
+      <c r="CJ1" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="CK1" s="50"/>
-      <c r="CL1" s="50"/>
-      <c r="CN1" s="50" t="s">
+      <c r="CK1" s="49"/>
+      <c r="CL1" s="49"/>
+      <c r="CN1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="CO1" s="50"/>
-      <c r="CP1" s="50"/>
-      <c r="CR1" s="58" t="s">
+      <c r="CO1" s="49"/>
+      <c r="CP1" s="49"/>
+      <c r="CR1" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="CS1" s="58"/>
-      <c r="CT1" s="58"/>
-      <c r="CV1" s="58" t="s">
+      <c r="CS1" s="57"/>
+      <c r="CT1" s="57"/>
+      <c r="CV1" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="CW1" s="58"/>
-      <c r="CX1" s="58"/>
-      <c r="CZ1" s="50" t="s">
+      <c r="CW1" s="57"/>
+      <c r="CX1" s="57"/>
+      <c r="CZ1" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="DA1" s="50"/>
-      <c r="DB1" s="50"/>
-      <c r="DD1" s="50" t="s">
+      <c r="DA1" s="49"/>
+      <c r="DB1" s="49"/>
+      <c r="DD1" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="DE1" s="50"/>
-      <c r="DF1" s="50"/>
-      <c r="DH1" s="50" t="s">
+      <c r="DE1" s="49"/>
+      <c r="DF1" s="49"/>
+      <c r="DH1" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="DI1" s="50"/>
-      <c r="DJ1" s="50"/>
-      <c r="DL1" s="50" t="s">
+      <c r="DI1" s="49"/>
+      <c r="DJ1" s="49"/>
+      <c r="DL1" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="DM1" s="50"/>
-      <c r="DN1" s="50"/>
-      <c r="DP1" s="50" t="s">
+      <c r="DM1" s="49"/>
+      <c r="DN1" s="49"/>
+      <c r="DP1" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="DQ1" s="50"/>
-      <c r="DR1" s="50"/>
-      <c r="DT1" s="50" t="s">
+      <c r="DQ1" s="49"/>
+      <c r="DR1" s="49"/>
+      <c r="DT1" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="DU1" s="50"/>
-      <c r="DV1" s="50"/>
-      <c r="DX1" s="50" t="s">
+      <c r="DU1" s="49"/>
+      <c r="DV1" s="49"/>
+      <c r="DX1" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="DY1" s="50"/>
-      <c r="DZ1" s="50"/>
+      <c r="DY1" s="49"/>
+      <c r="DZ1" s="49"/>
       <c r="EA1" s="3"/>
-      <c r="EB1" s="50" t="s">
+      <c r="EB1" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="EC1" s="50"/>
-      <c r="ED1" s="50"/>
-      <c r="EF1" s="50" t="s">
+      <c r="EC1" s="49"/>
+      <c r="ED1" s="49"/>
+      <c r="EF1" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="EG1" s="50"/>
-      <c r="EH1" s="50"/>
-      <c r="EI1" s="50"/>
-      <c r="EJ1" s="50"/>
-      <c r="EK1" s="50"/>
-      <c r="EL1" s="50"/>
-      <c r="EM1" s="50"/>
-      <c r="EN1" s="50"/>
-      <c r="EO1" s="50"/>
-      <c r="EP1" s="50"/>
-      <c r="EQ1" s="50"/>
-      <c r="ER1" s="50"/>
-      <c r="ES1" s="50"/>
-      <c r="EU1" s="50" t="s">
+      <c r="EG1" s="62"/>
+      <c r="EH1" s="62"/>
+      <c r="EI1" s="62"/>
+      <c r="EJ1" s="62"/>
+      <c r="EK1" s="62"/>
+      <c r="EL1" s="62"/>
+      <c r="EM1" s="62"/>
+      <c r="EN1" s="62"/>
+      <c r="EO1" s="62"/>
+      <c r="EP1" s="62"/>
+      <c r="EQ1" s="62"/>
+      <c r="ER1" s="62"/>
+      <c r="ES1" s="62"/>
+      <c r="EU1" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="EV1" s="50"/>
-      <c r="EW1" s="50"/>
-      <c r="EX1" s="50"/>
-      <c r="EY1" s="50"/>
-      <c r="EZ1" s="50"/>
-      <c r="FA1" s="50"/>
-      <c r="FB1" s="50"/>
-      <c r="FC1" s="50"/>
-      <c r="FD1" s="50"/>
-      <c r="FE1" s="50"/>
-      <c r="FF1" s="50"/>
-      <c r="FG1" s="50"/>
-      <c r="FH1" s="50"/>
+      <c r="EV1" s="49"/>
+      <c r="EW1" s="49"/>
+      <c r="EX1" s="49"/>
+      <c r="EY1" s="49"/>
+      <c r="EZ1" s="49"/>
+      <c r="FA1" s="49"/>
+      <c r="FB1" s="49"/>
+      <c r="FC1" s="49"/>
+      <c r="FD1" s="49"/>
+      <c r="FE1" s="49"/>
+      <c r="FF1" s="49"/>
+      <c r="FG1" s="49"/>
+      <c r="FH1" s="49"/>
     </row>
-    <row r="2" spans="2:164" x14ac:dyDescent="0.3">
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
+    <row r="2" spans="2:164" x14ac:dyDescent="0.25">
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
       <c r="V2" s="4"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="51"/>
-      <c r="AN2" s="51"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="51"/>
-      <c r="AS2" s="51"/>
-      <c r="AT2" s="51"/>
-      <c r="AU2" s="51"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="51"/>
-      <c r="AX2" s="51"/>
-      <c r="AY2" s="51"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="50"/>
+      <c r="AS2" s="50"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
       <c r="AZ2" s="3"/>
-      <c r="BB2" s="51"/>
-      <c r="BC2" s="51"/>
-      <c r="BD2" s="51"/>
-      <c r="BE2" s="51"/>
-      <c r="BF2" s="51"/>
-      <c r="BG2" s="51"/>
-      <c r="BH2" s="51"/>
-      <c r="BI2" s="51"/>
-      <c r="BJ2" s="51"/>
-      <c r="BK2" s="51"/>
-      <c r="BL2" s="51"/>
-      <c r="BM2" s="51"/>
-      <c r="BN2" s="51"/>
-      <c r="BO2" s="51"/>
-      <c r="BP2" s="51"/>
-      <c r="BQ2" s="51"/>
-      <c r="BR2" s="51"/>
-      <c r="BS2" s="51"/>
-      <c r="BT2" s="51"/>
-      <c r="BU2" s="51"/>
+      <c r="BB2" s="50"/>
+      <c r="BC2" s="50"/>
+      <c r="BD2" s="50"/>
+      <c r="BE2" s="50"/>
+      <c r="BF2" s="50"/>
+      <c r="BG2" s="50"/>
+      <c r="BH2" s="50"/>
+      <c r="BI2" s="50"/>
+      <c r="BJ2" s="50"/>
+      <c r="BK2" s="50"/>
+      <c r="BL2" s="50"/>
+      <c r="BM2" s="50"/>
+      <c r="BN2" s="50"/>
+      <c r="BO2" s="50"/>
+      <c r="BP2" s="50"/>
+      <c r="BQ2" s="50"/>
+      <c r="BR2" s="50"/>
+      <c r="BS2" s="50"/>
+      <c r="BT2" s="50"/>
+      <c r="BU2" s="50"/>
       <c r="BV2" s="3"/>
-      <c r="BX2" s="50"/>
-      <c r="BY2" s="50"/>
-      <c r="BZ2" s="50"/>
-      <c r="CB2" s="50"/>
-      <c r="CC2" s="50"/>
-      <c r="CD2" s="50"/>
-      <c r="CF2" s="50"/>
-      <c r="CG2" s="50"/>
-      <c r="CH2" s="50"/>
-      <c r="CJ2" s="50"/>
-      <c r="CK2" s="50"/>
-      <c r="CL2" s="50"/>
-      <c r="CN2" s="50"/>
-      <c r="CO2" s="50"/>
-      <c r="CP2" s="50"/>
-      <c r="CR2" s="58"/>
-      <c r="CS2" s="58"/>
-      <c r="CT2" s="58"/>
-      <c r="CV2" s="58"/>
-      <c r="CW2" s="58"/>
-      <c r="CX2" s="58"/>
-      <c r="CZ2" s="50"/>
-      <c r="DA2" s="50"/>
-      <c r="DB2" s="50"/>
-      <c r="DD2" s="50"/>
-      <c r="DE2" s="50"/>
-      <c r="DF2" s="50"/>
-      <c r="DH2" s="50"/>
-      <c r="DI2" s="50"/>
-      <c r="DJ2" s="50"/>
-      <c r="DL2" s="50"/>
-      <c r="DM2" s="50"/>
-      <c r="DN2" s="50"/>
-      <c r="DP2" s="50"/>
-      <c r="DQ2" s="50"/>
-      <c r="DR2" s="50"/>
-      <c r="DT2" s="50"/>
-      <c r="DU2" s="50"/>
-      <c r="DV2" s="50"/>
-      <c r="DX2" s="50"/>
-      <c r="DY2" s="50"/>
-      <c r="DZ2" s="50"/>
+      <c r="BX2" s="49"/>
+      <c r="BY2" s="49"/>
+      <c r="BZ2" s="49"/>
+      <c r="CB2" s="49"/>
+      <c r="CC2" s="49"/>
+      <c r="CD2" s="49"/>
+      <c r="CF2" s="49"/>
+      <c r="CG2" s="49"/>
+      <c r="CH2" s="49"/>
+      <c r="CJ2" s="49"/>
+      <c r="CK2" s="49"/>
+      <c r="CL2" s="49"/>
+      <c r="CN2" s="49"/>
+      <c r="CO2" s="49"/>
+      <c r="CP2" s="49"/>
+      <c r="CR2" s="57"/>
+      <c r="CS2" s="57"/>
+      <c r="CT2" s="57"/>
+      <c r="CV2" s="57"/>
+      <c r="CW2" s="57"/>
+      <c r="CX2" s="57"/>
+      <c r="CZ2" s="49"/>
+      <c r="DA2" s="49"/>
+      <c r="DB2" s="49"/>
+      <c r="DD2" s="49"/>
+      <c r="DE2" s="49"/>
+      <c r="DF2" s="49"/>
+      <c r="DH2" s="49"/>
+      <c r="DI2" s="49"/>
+      <c r="DJ2" s="49"/>
+      <c r="DL2" s="49"/>
+      <c r="DM2" s="49"/>
+      <c r="DN2" s="49"/>
+      <c r="DP2" s="49"/>
+      <c r="DQ2" s="49"/>
+      <c r="DR2" s="49"/>
+      <c r="DT2" s="49"/>
+      <c r="DU2" s="49"/>
+      <c r="DV2" s="49"/>
+      <c r="DX2" s="49"/>
+      <c r="DY2" s="49"/>
+      <c r="DZ2" s="49"/>
       <c r="EA2" s="3"/>
-      <c r="EB2" s="50"/>
-      <c r="EC2" s="50"/>
-      <c r="ED2" s="50"/>
-      <c r="EF2" s="51"/>
-      <c r="EG2" s="51"/>
-      <c r="EH2" s="51"/>
-      <c r="EI2" s="51"/>
-      <c r="EJ2" s="51"/>
-      <c r="EK2" s="51"/>
-      <c r="EL2" s="51"/>
-      <c r="EM2" s="51"/>
-      <c r="EN2" s="51"/>
-      <c r="EO2" s="51"/>
-      <c r="EP2" s="51"/>
-      <c r="EQ2" s="51"/>
-      <c r="ER2" s="51"/>
-      <c r="ES2" s="51"/>
-      <c r="EU2" s="51"/>
-      <c r="EV2" s="51"/>
-      <c r="EW2" s="51"/>
-      <c r="EX2" s="51"/>
-      <c r="EY2" s="51"/>
-      <c r="EZ2" s="51"/>
-      <c r="FA2" s="51"/>
-      <c r="FB2" s="51"/>
-      <c r="FC2" s="51"/>
-      <c r="FD2" s="51"/>
-      <c r="FE2" s="51"/>
-      <c r="FF2" s="51"/>
-      <c r="FG2" s="51"/>
-      <c r="FH2" s="51"/>
+      <c r="EB2" s="49"/>
+      <c r="EC2" s="49"/>
+      <c r="ED2" s="49"/>
+      <c r="EF2" s="63"/>
+      <c r="EG2" s="63"/>
+      <c r="EH2" s="63"/>
+      <c r="EI2" s="63"/>
+      <c r="EJ2" s="63"/>
+      <c r="EK2" s="63"/>
+      <c r="EL2" s="63"/>
+      <c r="EM2" s="63"/>
+      <c r="EN2" s="63"/>
+      <c r="EO2" s="63"/>
+      <c r="EP2" s="63"/>
+      <c r="EQ2" s="63"/>
+      <c r="ER2" s="63"/>
+      <c r="ES2" s="63"/>
+      <c r="EU2" s="50"/>
+      <c r="EV2" s="50"/>
+      <c r="EW2" s="50"/>
+      <c r="EX2" s="50"/>
+      <c r="EY2" s="50"/>
+      <c r="EZ2" s="50"/>
+      <c r="FA2" s="50"/>
+      <c r="FB2" s="50"/>
+      <c r="FC2" s="50"/>
+      <c r="FD2" s="50"/>
+      <c r="FE2" s="50"/>
+      <c r="FF2" s="50"/>
+      <c r="FG2" s="50"/>
+      <c r="FH2" s="50"/>
     </row>
-    <row r="3" spans="2:164" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+    <row r="3" spans="2:164" x14ac:dyDescent="0.25">
+      <c r="B3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53">
+      <c r="C3" s="51"/>
+      <c r="D3" s="51">
         <v>0</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="56">
+      <c r="E3" s="51"/>
+      <c r="F3" s="54">
         <v>1</v>
       </c>
-      <c r="G3" s="55"/>
-      <c r="H3" s="53">
+      <c r="G3" s="53"/>
+      <c r="H3" s="51">
         <v>2</v>
       </c>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56">
+      <c r="I3" s="51"/>
+      <c r="J3" s="54">
         <v>3</v>
       </c>
-      <c r="K3" s="55"/>
-      <c r="L3" s="53">
+      <c r="K3" s="53"/>
+      <c r="L3" s="51">
         <v>4</v>
       </c>
-      <c r="M3" s="53"/>
-      <c r="N3" s="56">
+      <c r="M3" s="51"/>
+      <c r="N3" s="54">
         <v>5</v>
       </c>
-      <c r="O3" s="55"/>
-      <c r="P3" s="56">
+      <c r="O3" s="53"/>
+      <c r="P3" s="54">
         <v>6</v>
       </c>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="53" t="s">
+      <c r="Q3" s="53"/>
+      <c r="R3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="53"/>
-      <c r="T3" s="60" t="s">
+      <c r="S3" s="51"/>
+      <c r="T3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="U3" s="53" t="s">
+      <c r="U3" s="51" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="36"/>
@@ -1777,89 +1876,89 @@
       <c r="AD3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AF3" s="53" t="s">
+      <c r="AF3" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53">
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="51">
         <v>0</v>
       </c>
-      <c r="AI3" s="53"/>
-      <c r="AJ3" s="56">
+      <c r="AI3" s="51"/>
+      <c r="AJ3" s="54">
         <v>1</v>
       </c>
-      <c r="AK3" s="55"/>
-      <c r="AL3" s="53">
+      <c r="AK3" s="53"/>
+      <c r="AL3" s="51">
         <v>2</v>
       </c>
-      <c r="AM3" s="53"/>
-      <c r="AN3" s="56">
+      <c r="AM3" s="51"/>
+      <c r="AN3" s="54">
         <v>3</v>
       </c>
-      <c r="AO3" s="55"/>
-      <c r="AP3" s="53">
+      <c r="AO3" s="53"/>
+      <c r="AP3" s="51">
         <v>4</v>
       </c>
-      <c r="AQ3" s="53"/>
-      <c r="AR3" s="56">
+      <c r="AQ3" s="51"/>
+      <c r="AR3" s="54">
         <v>5</v>
       </c>
-      <c r="AS3" s="55"/>
-      <c r="AT3" s="56">
+      <c r="AS3" s="53"/>
+      <c r="AT3" s="54">
         <v>6</v>
       </c>
-      <c r="AU3" s="55"/>
-      <c r="AV3" s="53" t="s">
+      <c r="AU3" s="53"/>
+      <c r="AV3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="AW3" s="53"/>
-      <c r="AX3" s="60" t="s">
+      <c r="AW3" s="51"/>
+      <c r="AX3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="AY3" s="53" t="s">
+      <c r="AY3" s="51" t="s">
         <v>12</v>
       </c>
       <c r="AZ3" s="35"/>
-      <c r="BB3" s="53" t="s">
+      <c r="BB3" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="BC3" s="53"/>
-      <c r="BD3" s="53" t="s">
+      <c r="BC3" s="51"/>
+      <c r="BD3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="BE3" s="53"/>
-      <c r="BF3" s="56" t="s">
+      <c r="BE3" s="51"/>
+      <c r="BF3" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="BG3" s="55"/>
-      <c r="BH3" s="53" t="s">
+      <c r="BG3" s="53"/>
+      <c r="BH3" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="BI3" s="53"/>
-      <c r="BJ3" s="56" t="s">
+      <c r="BI3" s="51"/>
+      <c r="BJ3" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="BK3" s="55"/>
-      <c r="BL3" s="53" t="s">
+      <c r="BK3" s="53"/>
+      <c r="BL3" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="BM3" s="53"/>
-      <c r="BN3" s="56" t="s">
+      <c r="BM3" s="51"/>
+      <c r="BN3" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="BO3" s="55"/>
-      <c r="BP3" s="56" t="s">
+      <c r="BO3" s="53"/>
+      <c r="BP3" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="BQ3" s="55"/>
-      <c r="BR3" s="53" t="s">
+      <c r="BQ3" s="53"/>
+      <c r="BR3" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="BS3" s="53"/>
-      <c r="BT3" s="60" t="s">
+      <c r="BS3" s="51"/>
+      <c r="BT3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="BU3" s="53" t="s">
+      <c r="BU3" s="51" t="s">
         <v>12</v>
       </c>
       <c r="BV3" s="35"/>
@@ -1999,70 +2098,70 @@
       <c r="ED3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="EF3" s="53" t="s">
+      <c r="EF3" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="EG3" s="53" t="s">
+      <c r="EG3" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="EH3" s="55"/>
-      <c r="EI3" s="53" t="s">
+      <c r="EH3" s="65"/>
+      <c r="EI3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="EJ3" s="55"/>
-      <c r="EK3" s="56" t="s">
+      <c r="EJ3" s="65"/>
+      <c r="EK3" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="EL3" s="55"/>
-      <c r="EM3" s="53" t="s">
+      <c r="EL3" s="65"/>
+      <c r="EM3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="EN3" s="55"/>
-      <c r="EO3" s="53" t="s">
+      <c r="EN3" s="65"/>
+      <c r="EO3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="EP3" s="53"/>
-      <c r="EQ3" s="53" t="s">
+      <c r="EP3" s="64"/>
+      <c r="EQ3" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="ER3" s="49" t="s">
+      <c r="ER3" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="ES3" s="49"/>
-      <c r="EU3" s="53" t="s">
+      <c r="ES3" s="67"/>
+      <c r="EU3" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="EV3" s="53" t="s">
+      <c r="EV3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="EW3" s="55"/>
-      <c r="EX3" s="53" t="s">
+      <c r="EW3" s="53"/>
+      <c r="EX3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="EY3" s="55"/>
-      <c r="EZ3" s="56" t="s">
+      <c r="EY3" s="53"/>
+      <c r="EZ3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="FA3" s="55"/>
-      <c r="FB3" s="53" t="s">
+      <c r="FA3" s="53"/>
+      <c r="FB3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="FC3" s="55"/>
-      <c r="FD3" s="53" t="s">
+      <c r="FC3" s="53"/>
+      <c r="FD3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="FE3" s="53"/>
-      <c r="FF3" s="53" t="s">
+      <c r="FE3" s="51"/>
+      <c r="FF3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="FG3" s="49" t="s">
+      <c r="FG3" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="FH3" s="49"/>
+      <c r="FH3" s="55"/>
     </row>
-    <row r="4" spans="2:164" x14ac:dyDescent="0.3">
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
+    <row r="4" spans="2:164" x14ac:dyDescent="0.25">
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
       <c r="D4" s="5" t="s">
         <v>0</v>
       </c>
@@ -2111,8 +2210,8 @@
       <c r="S4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="T4" s="61"/>
-      <c r="U4" s="54"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="52"/>
       <c r="V4" s="36"/>
       <c r="X4" s="9" t="s">
         <v>16</v>
@@ -2132,8 +2231,8 @@
       <c r="AD4" s="23">
         <v>0.75167590922251204</v>
       </c>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="54"/>
+      <c r="AF4" s="52"/>
+      <c r="AG4" s="52"/>
       <c r="AH4" s="5" t="s">
         <v>0</v>
       </c>
@@ -2182,11 +2281,11 @@
       <c r="AW4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AX4" s="61"/>
-      <c r="AY4" s="54"/>
+      <c r="AX4" s="60"/>
+      <c r="AY4" s="52"/>
       <c r="AZ4" s="35"/>
-      <c r="BB4" s="54"/>
-      <c r="BC4" s="54"/>
+      <c r="BB4" s="52"/>
+      <c r="BC4" s="52"/>
       <c r="BD4" s="5" t="s">
         <v>0</v>
       </c>
@@ -2235,8 +2334,8 @@
       <c r="BS4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BT4" s="61"/>
-      <c r="BU4" s="54"/>
+      <c r="BT4" s="60"/>
+      <c r="BU4" s="52"/>
       <c r="BV4" s="35"/>
       <c r="BX4" s="9" t="s">
         <v>28</v>
@@ -2373,45 +2472,45 @@
       <c r="ED4" s="11">
         <v>3.4381467387676098E-2</v>
       </c>
-      <c r="EF4" s="54"/>
-      <c r="EG4" s="5" t="s">
+      <c r="EF4" s="68"/>
+      <c r="EG4" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="EH4" s="8" t="s">
+      <c r="EH4" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="EI4" s="5" t="s">
+      <c r="EI4" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="EJ4" s="8" t="s">
+      <c r="EJ4" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="EK4" s="7" t="s">
+      <c r="EK4" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="EL4" s="8" t="s">
+      <c r="EL4" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="EM4" s="5" t="s">
+      <c r="EM4" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="EN4" s="8" t="s">
+      <c r="EN4" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="EO4" s="5" t="s">
+      <c r="EO4" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="EP4" s="6" t="s">
+      <c r="EP4" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="EQ4" s="54"/>
-      <c r="ER4" s="5" t="s">
+      <c r="EQ4" s="68"/>
+      <c r="ER4" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="ES4" s="6" t="s">
+      <c r="ES4" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="EU4" s="54"/>
+      <c r="EU4" s="52"/>
       <c r="EV4" s="5" t="s">
         <v>0</v>
       </c>
@@ -2442,7 +2541,7 @@
       <c r="FE4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="FF4" s="54"/>
+      <c r="FF4" s="52"/>
       <c r="FG4" s="5" t="s">
         <v>0</v>
       </c>
@@ -2450,8 +2549,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:164" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="57" t="s">
+    <row r="5" spans="2:164" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="56" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -2505,7 +2604,7 @@
       <c r="S5" s="11">
         <v>0.58051529790660195</v>
       </c>
-      <c r="T5" s="52" t="s">
+      <c r="T5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="U5" s="10">
@@ -2534,7 +2633,7 @@
       <c r="AD5" s="24">
         <v>0.24832409077748799</v>
       </c>
-      <c r="AF5" s="57" t="s">
+      <c r="AF5" s="56" t="s">
         <v>23</v>
       </c>
       <c r="AG5" s="9" t="s">
@@ -2588,7 +2687,7 @@
       <c r="AW5" s="11">
         <v>0.59107142857142903</v>
       </c>
-      <c r="AX5" s="52" t="s">
+      <c r="AX5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="AY5" s="10">
@@ -2599,7 +2698,7 @@
         <f>AY5/AY10</f>
         <v>0.50755973190229131</v>
       </c>
-      <c r="BB5" s="57" t="s">
+      <c r="BB5" s="56" t="s">
         <v>23</v>
       </c>
       <c r="BC5" s="9" t="s">
@@ -2653,7 +2752,7 @@
       <c r="BS5" s="11">
         <v>0.59107142857142903</v>
       </c>
-      <c r="BT5" s="52" t="s">
+      <c r="BT5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="BU5" s="10">
@@ -2799,47 +2898,47 @@
       <c r="ED5" s="4">
         <v>8.5831274895965495E-2</v>
       </c>
-      <c r="EF5" s="9" t="s">
+      <c r="EF5" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="EG5" s="22">
+      <c r="EG5" s="74">
         <v>517</v>
       </c>
-      <c r="EH5" s="39">
+      <c r="EH5" s="75">
         <v>0.33462783171520999</v>
       </c>
-      <c r="EI5" s="22">
+      <c r="EI5" s="74">
         <v>819</v>
       </c>
-      <c r="EJ5" s="39">
+      <c r="EJ5" s="75">
         <v>0.212341197822142</v>
       </c>
-      <c r="EK5" s="42">
+      <c r="EK5" s="76">
         <v>1230</v>
       </c>
-      <c r="EL5" s="39">
+      <c r="EL5" s="75">
         <v>0.102585487906589</v>
       </c>
-      <c r="EM5" s="22">
+      <c r="EM5" s="74">
         <v>1492</v>
       </c>
-      <c r="EN5" s="39">
+      <c r="EN5" s="75">
         <v>5.6697700931027897E-2</v>
       </c>
-      <c r="EO5" s="22">
+      <c r="EO5" s="74">
         <v>38</v>
       </c>
-      <c r="EP5" s="23">
+      <c r="EP5" s="77">
         <v>3.0894308943089401E-2</v>
       </c>
-      <c r="EQ5" s="52" t="s">
+      <c r="EQ5" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="ER5" s="3">
+      <c r="ER5" s="79">
         <f>SUM(EG5,EI5,EK5,EM5,EO5)</f>
         <v>4096</v>
       </c>
-      <c r="ES5" s="4">
+      <c r="ES5" s="80">
         <f>ER5/ER10</f>
         <v>9.1149831987004035E-2</v>
       </c>
@@ -2876,7 +2975,7 @@
       <c r="FE5" s="23">
         <v>9.27734375E-3</v>
       </c>
-      <c r="FF5" s="52" t="s">
+      <c r="FF5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="FG5" s="3">
@@ -2888,8 +2987,8 @@
         <v>9.1149831987004035E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:164" x14ac:dyDescent="0.3">
-      <c r="B6" s="58"/>
+    <row r="6" spans="2:164" x14ac:dyDescent="0.25">
+      <c r="B6" s="57"/>
       <c r="C6" t="s">
         <v>3</v>
       </c>
@@ -2941,7 +3040,7 @@
       <c r="S6" s="4">
         <v>0.16505636070853499</v>
       </c>
-      <c r="T6" s="50"/>
+      <c r="T6" s="49"/>
       <c r="U6" s="3">
         <f t="shared" ref="U6:U9" si="0">SUM(D6,F6,H6,J6,L6,N6,P6,R6)</f>
         <v>12280</v>
@@ -2972,7 +3071,7 @@
         <f>SUM(AD4:AD5)</f>
         <v>1</v>
       </c>
-      <c r="AF6" s="58"/>
+      <c r="AF6" s="57"/>
       <c r="AG6" t="s">
         <v>3</v>
       </c>
@@ -3024,7 +3123,7 @@
       <c r="AW6" s="4">
         <v>5.7142857142857099E-2</v>
       </c>
-      <c r="AX6" s="50"/>
+      <c r="AX6" s="49"/>
       <c r="AY6" s="3">
         <f>SUM(AH6,AJ6,AL6,AN6,AP6,AR6,AT6,AV6)</f>
         <v>2533</v>
@@ -3033,7 +3132,7 @@
         <f>AY6/AY10</f>
         <v>5.6402948184105635E-2</v>
       </c>
-      <c r="BB6" s="58"/>
+      <c r="BB6" s="57"/>
       <c r="BC6" t="s">
         <v>3</v>
       </c>
@@ -3085,7 +3184,7 @@
       <c r="BS6" s="4">
         <v>5.7142857142857099E-2</v>
       </c>
-      <c r="BT6" s="50"/>
+      <c r="BT6" s="49"/>
       <c r="BU6" s="3">
         <f>SUM(BD6,BF6,BH6,BJ6,BL6,BN6,BP6,BR6)</f>
         <v>2533</v>
@@ -3235,45 +3334,45 @@
       <c r="ED6" s="4">
         <v>0.26681798962992598</v>
       </c>
-      <c r="EF6" t="s">
+      <c r="EF6" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="EG6" s="1">
+      <c r="EG6" s="82">
         <v>855</v>
       </c>
-      <c r="EH6" s="40">
+      <c r="EH6" s="83">
         <v>0.55339805825242705</v>
       </c>
-      <c r="EI6" s="1">
+      <c r="EI6" s="82">
         <v>2238</v>
       </c>
-      <c r="EJ6" s="40">
+      <c r="EJ6" s="83">
         <v>0.580243712730101</v>
       </c>
-      <c r="EK6" s="43">
+      <c r="EK6" s="84">
         <v>6536</v>
       </c>
-      <c r="EL6" s="40">
+      <c r="EL6" s="83">
         <v>0.54512093411175999</v>
       </c>
-      <c r="EM6" s="1">
+      <c r="EM6" s="82">
         <v>8012</v>
       </c>
-      <c r="EN6" s="40">
+      <c r="EN6" s="83">
         <v>0.30446513395401897</v>
       </c>
-      <c r="EO6" s="1">
+      <c r="EO6" s="82">
         <v>96</v>
       </c>
-      <c r="EP6" s="2">
+      <c r="EP6" s="85">
         <v>7.8048780487804906E-2</v>
       </c>
-      <c r="EQ6" s="50"/>
-      <c r="ER6" s="3">
+      <c r="EQ6" s="62"/>
+      <c r="ER6" s="79">
         <f t="shared" ref="ER6:ER37" si="1">SUM(EG6,EI6,EK6,EM6,EO6)</f>
         <v>17737</v>
       </c>
-      <c r="ES6" s="4">
+      <c r="ES6" s="80">
         <f>ER6/ER10</f>
         <v>0.39470814696130135</v>
       </c>
@@ -3310,7 +3409,7 @@
       <c r="FE6" s="2">
         <v>5.4124147262784002E-3</v>
       </c>
-      <c r="FF6" s="50"/>
+      <c r="FF6" s="49"/>
       <c r="FG6" s="3">
         <f t="shared" ref="FG6:FG10" si="2">SUM(EV6,EX6,EZ6,FB6,FD6)</f>
         <v>17737</v>
@@ -3320,8 +3419,8 @@
         <v>0.39470814696130135</v>
       </c>
     </row>
-    <row r="7" spans="2:164" x14ac:dyDescent="0.3">
-      <c r="B7" s="58"/>
+    <row r="7" spans="2:164" x14ac:dyDescent="0.25">
+      <c r="B7" s="57"/>
       <c r="C7" t="s">
         <v>4</v>
       </c>
@@ -3373,7 +3472,7 @@
       <c r="S7" s="4">
         <v>8.0515297906602196E-3</v>
       </c>
-      <c r="T7" s="50"/>
+      <c r="T7" s="49"/>
       <c r="U7" s="3">
         <f t="shared" si="0"/>
         <v>11020</v>
@@ -3382,7 +3481,7 @@
         <f>U7/U10</f>
         <v>0.24531956100710137</v>
       </c>
-      <c r="AF7" s="58"/>
+      <c r="AF7" s="57"/>
       <c r="AG7" t="s">
         <v>4</v>
       </c>
@@ -3434,7 +3533,7 @@
       <c r="AW7" s="4">
         <v>5.3571428571428598E-3</v>
       </c>
-      <c r="AX7" s="50"/>
+      <c r="AX7" s="49"/>
       <c r="AY7" s="3">
         <f>SUM(AH7,AJ7,AL7,AN7,AP7,AR7,AT7,AV7)</f>
         <v>1411</v>
@@ -3443,7 +3542,7 @@
         <f>AY7/AY10</f>
         <v>3.141909194148166E-2</v>
       </c>
-      <c r="BB7" s="58"/>
+      <c r="BB7" s="57"/>
       <c r="BC7" t="s">
         <v>4</v>
       </c>
@@ -3495,7 +3594,7 @@
       <c r="BS7" s="4">
         <v>5.3571428571428598E-3</v>
       </c>
-      <c r="BT7" s="50"/>
+      <c r="BT7" s="49"/>
       <c r="BU7" s="3">
         <f>SUM(BD7,BF7,BH7,BJ7,BL7,BN7,BP7,BR7)</f>
         <v>1411</v>
@@ -3616,45 +3715,45 @@
       <c r="ED7" s="4">
         <v>0.58559761443799097</v>
       </c>
-      <c r="EF7" t="s">
+      <c r="EF7" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="EG7" s="1">
+      <c r="EG7" s="82">
         <v>105</v>
       </c>
-      <c r="EH7" s="40">
+      <c r="EH7" s="83">
         <v>6.7961165048543701E-2</v>
       </c>
-      <c r="EI7" s="1">
+      <c r="EI7" s="82">
         <v>591</v>
       </c>
-      <c r="EJ7" s="40">
+      <c r="EJ7" s="83">
         <v>0.15322789732953099</v>
       </c>
-      <c r="EK7" s="43">
+      <c r="EK7" s="84">
         <v>2748</v>
       </c>
-      <c r="EL7" s="40">
+      <c r="EL7" s="83">
         <v>0.229190992493745</v>
       </c>
-      <c r="EM7" s="1">
+      <c r="EM7" s="82">
         <v>9453</v>
       </c>
-      <c r="EN7" s="40">
+      <c r="EN7" s="83">
         <v>0.359224776743302</v>
       </c>
-      <c r="EO7" s="1">
+      <c r="EO7" s="82">
         <v>477</v>
       </c>
-      <c r="EP7" s="2">
+      <c r="EP7" s="85">
         <v>0.38780487804878</v>
       </c>
-      <c r="EQ7" s="50"/>
-      <c r="ER7" s="3">
+      <c r="EQ7" s="62"/>
+      <c r="ER7" s="79">
         <f t="shared" si="1"/>
         <v>13374</v>
       </c>
-      <c r="ES7" s="4">
+      <c r="ES7" s="80">
         <f>ER7/ER10</f>
         <v>0.2976166633286601</v>
       </c>
@@ -3691,7 +3790,7 @@
       <c r="FE7" s="2">
         <v>3.5666218034993299E-2</v>
       </c>
-      <c r="FF7" s="50"/>
+      <c r="FF7" s="49"/>
       <c r="FG7" s="3">
         <f t="shared" si="2"/>
         <v>13374</v>
@@ -3701,8 +3800,8 @@
         <v>0.2976166633286601</v>
       </c>
     </row>
-    <row r="8" spans="2:164" x14ac:dyDescent="0.3">
-      <c r="B8" s="58"/>
+    <row r="8" spans="2:164" x14ac:dyDescent="0.25">
+      <c r="B8" s="57"/>
       <c r="C8" t="s">
         <v>5</v>
       </c>
@@ -3754,7 +3853,7 @@
       <c r="S8" s="4">
         <v>0.15942028985507201</v>
       </c>
-      <c r="T8" s="50"/>
+      <c r="T8" s="49"/>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
         <v>6415</v>
@@ -3763,7 +3862,7 @@
         <f>U8/U10</f>
         <v>0.14280625987845327</v>
       </c>
-      <c r="AF8" s="58"/>
+      <c r="AF8" s="57"/>
       <c r="AG8" t="s">
         <v>5</v>
       </c>
@@ -3815,7 +3914,7 @@
       <c r="AW8" s="4">
         <v>2.6785714285714302E-2</v>
       </c>
-      <c r="AX8" s="50"/>
+      <c r="AX8" s="49"/>
       <c r="AY8" s="3">
         <f>SUM(AH8,AJ8,AL8,AN8,AP8,AR8,AT8,AV8)</f>
         <v>2203</v>
@@ -3824,7 +3923,7 @@
         <f>AY8/AY10</f>
         <v>4.9054755171569174E-2</v>
       </c>
-      <c r="BB8" s="58"/>
+      <c r="BB8" s="57"/>
       <c r="BC8" t="s">
         <v>5</v>
       </c>
@@ -3876,7 +3975,7 @@
       <c r="BS8" s="4">
         <v>2.6785714285714302E-2</v>
       </c>
-      <c r="BT8" s="50"/>
+      <c r="BT8" s="49"/>
       <c r="BU8" s="3">
         <f>SUM(BD8,BF8,BH8,BJ8,BL8,BN8,BP8,BR8)</f>
         <v>2203</v>
@@ -3952,11 +4051,11 @@
         <f>SUM(DJ4:DJ7)</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="DL8" s="48" t="s">
+      <c r="DL8" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="DM8" s="48"/>
-      <c r="DN8" s="48"/>
+      <c r="DM8" s="61"/>
+      <c r="DN8" s="61"/>
       <c r="DP8" s="12" t="s">
         <v>6</v>
       </c>
@@ -3984,45 +4083,45 @@
       <c r="ED8" s="14">
         <v>2.7371653648441199E-2</v>
       </c>
-      <c r="EF8" t="s">
+      <c r="EF8" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="EG8" s="1">
+      <c r="EG8" s="82">
         <v>38</v>
       </c>
-      <c r="EH8" s="40">
+      <c r="EH8" s="83">
         <v>2.4595469255663398E-2</v>
       </c>
-      <c r="EI8" s="1">
+      <c r="EI8" s="82">
         <v>109</v>
       </c>
-      <c r="EJ8" s="40">
+      <c r="EJ8" s="83">
         <v>2.82603059372569E-2</v>
       </c>
-      <c r="EK8" s="43">
+      <c r="EK8" s="84">
         <v>744</v>
       </c>
-      <c r="EL8" s="40">
+      <c r="EL8" s="83">
         <v>6.2051709758131797E-2</v>
       </c>
-      <c r="EM8" s="1">
+      <c r="EM8" s="82">
         <v>5158</v>
       </c>
-      <c r="EN8" s="40">
+      <c r="EN8" s="83">
         <v>0.19600988029640901</v>
       </c>
-      <c r="EO8" s="1">
+      <c r="EO8" s="82">
         <v>558</v>
       </c>
-      <c r="EP8" s="2">
+      <c r="EP8" s="85">
         <v>0.45365853658536598</v>
       </c>
-      <c r="EQ8" s="50"/>
-      <c r="ER8" s="3">
+      <c r="EQ8" s="62"/>
+      <c r="ER8" s="79">
         <f t="shared" si="1"/>
         <v>6607</v>
       </c>
-      <c r="ES8" s="4">
+      <c r="ES8" s="80">
         <f>ER8/ER10</f>
         <v>0.14702806150833389</v>
       </c>
@@ -4059,7 +4158,7 @@
       <c r="FE8" s="2">
         <v>8.4455880127137894E-2</v>
       </c>
-      <c r="FF8" s="50"/>
+      <c r="FF8" s="49"/>
       <c r="FG8" s="3">
         <f t="shared" si="2"/>
         <v>6607</v>
@@ -4069,8 +4168,8 @@
         <v>0.14702806150833389</v>
       </c>
     </row>
-    <row r="9" spans="2:164" x14ac:dyDescent="0.3">
-      <c r="B9" s="59"/>
+    <row r="9" spans="2:164" x14ac:dyDescent="0.25">
+      <c r="B9" s="58"/>
       <c r="C9" s="12" t="s">
         <v>6</v>
       </c>
@@ -4122,7 +4221,7 @@
       <c r="S9" s="14">
         <v>8.6956521739130405E-2</v>
       </c>
-      <c r="T9" s="51"/>
+      <c r="T9" s="50"/>
       <c r="U9" s="13">
         <f t="shared" si="0"/>
         <v>5272</v>
@@ -4131,7 +4230,7 @@
         <f>U9/U10</f>
         <v>0.11736159034749895</v>
       </c>
-      <c r="AF9" s="59"/>
+      <c r="AF9" s="58"/>
       <c r="AG9" s="12" t="s">
         <v>6</v>
       </c>
@@ -4183,7 +4282,7 @@
       <c r="AW9" s="14">
         <v>0.31964285714285701</v>
       </c>
-      <c r="AX9" s="51"/>
+      <c r="AX9" s="50"/>
       <c r="AY9" s="13">
         <f>SUM(AH9,AJ9,AL9,AN9,AP9,AR9,AT9,AV9)</f>
         <v>15968</v>
@@ -4192,7 +4291,7 @@
         <f>AY9/AY10</f>
         <v>0.35556347280055223</v>
       </c>
-      <c r="BB9" s="59"/>
+      <c r="BB9" s="58"/>
       <c r="BC9" s="12" t="s">
         <v>6</v>
       </c>
@@ -4244,7 +4343,7 @@
       <c r="BS9" s="14">
         <v>0.31964285714285701</v>
       </c>
-      <c r="BT9" s="51"/>
+      <c r="BT9" s="50"/>
       <c r="BU9" s="13">
         <f>SUM(BD9,BF9,BH9,BJ9,BL9,BN9,BP9,BR9)</f>
         <v>15968</v>
@@ -4304,9 +4403,9 @@
         <f>SUM(DF4:DF8)</f>
         <v>1</v>
       </c>
-      <c r="DL9" s="48"/>
-      <c r="DM9" s="48"/>
-      <c r="DN9" s="48"/>
+      <c r="DL9" s="61"/>
+      <c r="DM9" s="61"/>
+      <c r="DN9" s="61"/>
       <c r="DP9" s="25" t="s">
         <v>12</v>
       </c>
@@ -4338,45 +4437,45 @@
         <f>SUM(ED4:ED8)</f>
         <v>0.99999999999999978</v>
       </c>
-      <c r="EF9" s="12" t="s">
+      <c r="EF9" s="86" t="s">
         <v>149</v>
       </c>
-      <c r="EG9" s="21">
+      <c r="EG9" s="87">
         <v>30</v>
       </c>
-      <c r="EH9" s="41">
+      <c r="EH9" s="88">
         <v>1.94174757281553E-2</v>
       </c>
-      <c r="EI9" s="21">
+      <c r="EI9" s="87">
         <v>100</v>
       </c>
-      <c r="EJ9" s="41">
+      <c r="EJ9" s="88">
         <v>2.5926886180969701E-2</v>
       </c>
-      <c r="EK9" s="44">
+      <c r="EK9" s="89">
         <v>732</v>
       </c>
-      <c r="EL9" s="41">
+      <c r="EL9" s="88">
         <v>6.1050875729774801E-2</v>
       </c>
-      <c r="EM9" s="21">
+      <c r="EM9" s="87">
         <v>2200</v>
       </c>
-      <c r="EN9" s="41">
+      <c r="EN9" s="88">
         <v>8.3602508075242304E-2</v>
       </c>
-      <c r="EO9" s="21">
+      <c r="EO9" s="87">
         <v>61</v>
       </c>
-      <c r="EP9" s="24">
+      <c r="EP9" s="90">
         <v>4.9593495934959299E-2</v>
       </c>
-      <c r="EQ9" s="51"/>
-      <c r="ER9" s="3">
+      <c r="EQ9" s="63"/>
+      <c r="ER9" s="79">
         <f t="shared" si="1"/>
         <v>3123</v>
       </c>
-      <c r="ES9" s="4">
+      <c r="ES9" s="80">
         <f>ER9/ER10</f>
         <v>6.9497296214700577E-2</v>
       </c>
@@ -4413,7 +4512,7 @@
       <c r="FE9" s="24">
         <v>1.95325008005123E-2</v>
       </c>
-      <c r="FF9" s="51"/>
+      <c r="FF9" s="50"/>
       <c r="FG9" s="3">
         <f t="shared" si="2"/>
         <v>3123</v>
@@ -4423,7 +4522,7 @@
         <v>6.9497296214700577E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:164" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:164" x14ac:dyDescent="0.25">
       <c r="U10" s="3">
         <f>SUM(U5:U9)</f>
         <v>44921</v>
@@ -4517,55 +4616,55 @@
       <c r="DZ10" s="2">
         <v>5.87489151478737E-3</v>
       </c>
-      <c r="EF10" t="s">
+      <c r="EF10" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="EG10" s="1">
+      <c r="EG10" s="82">
         <f>SUM(EG5:EG9)</f>
         <v>1545</v>
       </c>
-      <c r="EH10" s="2">
+      <c r="EH10" s="85">
         <f t="shared" ref="EH10:EP10" si="4">SUM(EH5:EH9)</f>
         <v>0.99999999999999933</v>
       </c>
-      <c r="EI10" s="46">
+      <c r="EI10" s="91">
         <f t="shared" si="4"/>
         <v>3857</v>
       </c>
-      <c r="EJ10" s="47">
+      <c r="EJ10" s="92">
         <f t="shared" si="4"/>
         <v>1.0000000000000007</v>
       </c>
-      <c r="EK10" s="1">
+      <c r="EK10" s="82">
         <f t="shared" si="4"/>
         <v>11990</v>
       </c>
-      <c r="EL10" s="2">
+      <c r="EL10" s="85">
         <f t="shared" si="4"/>
         <v>1.0000000000000007</v>
       </c>
-      <c r="EM10" s="46">
+      <c r="EM10" s="91">
         <f t="shared" si="4"/>
         <v>26315</v>
       </c>
-      <c r="EN10" s="47">
+      <c r="EN10" s="92">
         <f t="shared" si="4"/>
         <v>1.0000000000000002</v>
       </c>
-      <c r="EO10" s="1">
+      <c r="EO10" s="82">
         <f t="shared" si="4"/>
         <v>1230</v>
       </c>
-      <c r="EP10" s="2">
+      <c r="EP10" s="85">
         <f t="shared" si="4"/>
         <v>0.99999999999999956</v>
       </c>
-      <c r="EQ10" s="3"/>
-      <c r="ER10" s="29">
+      <c r="EQ10" s="79"/>
+      <c r="ER10" s="93">
         <f t="shared" si="1"/>
         <v>44937</v>
       </c>
-      <c r="ES10" s="30">
+      <c r="ES10" s="94">
         <f>SUM(ES5:ES9)</f>
         <v>1</v>
       </c>
@@ -4607,13 +4706,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:164" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:164" x14ac:dyDescent="0.25">
       <c r="BU11" s="3"/>
-      <c r="CB11" s="48" t="s">
+      <c r="CB11" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="CC11" s="48"/>
-      <c r="CD11" s="48"/>
+      <c r="CC11" s="61"/>
+      <c r="CD11" s="61"/>
       <c r="CR11" t="s">
         <v>54</v>
       </c>
@@ -4632,16 +4731,16 @@
       <c r="CX11" s="2">
         <v>1.9516211585107999E-2</v>
       </c>
-      <c r="CZ11" s="48" t="s">
+      <c r="CZ11" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="DA11" s="48"/>
-      <c r="DB11" s="48"/>
-      <c r="DD11" s="48" t="s">
+      <c r="DA11" s="61"/>
+      <c r="DB11" s="61"/>
+      <c r="DD11" s="61" t="s">
         <v>184</v>
       </c>
-      <c r="DE11" s="48"/>
-      <c r="DF11" s="48"/>
+      <c r="DE11" s="61"/>
+      <c r="DF11" s="61"/>
       <c r="DL11" s="9" t="s">
         <v>41</v>
       </c>
@@ -4693,7 +4792,7 @@
       <c r="EP11" s="23">
         <v>0</v>
       </c>
-      <c r="EQ11" s="52" t="s">
+      <c r="EQ11" s="48" t="s">
         <v>8</v>
       </c>
       <c r="ER11" s="3">
@@ -4737,7 +4836,7 @@
       <c r="FE11" s="23">
         <v>0</v>
       </c>
-      <c r="FF11" s="52" t="s">
+      <c r="FF11" s="48" t="s">
         <v>8</v>
       </c>
       <c r="FG11" s="3">
@@ -4749,10 +4848,10 @@
         <v>5.0292631906891875E-3</v>
       </c>
     </row>
-    <row r="12" spans="2:164" x14ac:dyDescent="0.3">
-      <c r="CB12" s="48"/>
-      <c r="CC12" s="48"/>
-      <c r="CD12" s="48"/>
+    <row r="12" spans="2:164" x14ac:dyDescent="0.25">
+      <c r="CB12" s="61"/>
+      <c r="CC12" s="61"/>
+      <c r="CD12" s="61"/>
       <c r="CR12" s="9" t="s">
         <v>55</v>
       </c>
@@ -4771,12 +4870,12 @@
       <c r="CX12" s="2">
         <v>9.8359926118788497E-3</v>
       </c>
-      <c r="CZ12" s="48"/>
-      <c r="DA12" s="48"/>
-      <c r="DB12" s="48"/>
-      <c r="DD12" s="48"/>
-      <c r="DE12" s="48"/>
-      <c r="DF12" s="48"/>
+      <c r="CZ12" s="61"/>
+      <c r="DA12" s="61"/>
+      <c r="DB12" s="61"/>
+      <c r="DD12" s="61"/>
+      <c r="DE12" s="61"/>
+      <c r="DF12" s="61"/>
       <c r="DL12" s="12" t="s">
         <v>42</v>
       </c>
@@ -4828,7 +4927,7 @@
       <c r="EP12" s="2">
         <v>0</v>
       </c>
-      <c r="EQ12" s="50"/>
+      <c r="EQ12" s="49"/>
       <c r="ER12" s="3">
         <f t="shared" si="1"/>
         <v>996</v>
@@ -4870,7 +4969,7 @@
       <c r="FE12" s="2">
         <v>0</v>
       </c>
-      <c r="FF12" s="50"/>
+      <c r="FF12" s="49"/>
       <c r="FG12" s="3">
         <f t="shared" ref="FG12:FG38" si="7">SUM(EV12,EX12,EZ12,FB12,FD12)</f>
         <v>996</v>
@@ -4880,7 +4979,7 @@
         <v>2.2164363442152345E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:164" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:164" x14ac:dyDescent="0.25">
       <c r="CB13" s="31" t="s">
         <v>73</v>
       </c>
@@ -4979,7 +5078,7 @@
       <c r="EP13" s="2">
         <v>2.4390243902438998E-3</v>
       </c>
-      <c r="EQ13" s="50"/>
+      <c r="EQ13" s="49"/>
       <c r="ER13" s="3">
         <f t="shared" si="1"/>
         <v>656</v>
@@ -5021,7 +5120,7 @@
       <c r="FE13" s="2">
         <v>4.5731707317073203E-3</v>
       </c>
-      <c r="FF13" s="50"/>
+      <c r="FF13" s="49"/>
       <c r="FG13" s="3">
         <f t="shared" si="7"/>
         <v>656</v>
@@ -5031,7 +5130,7 @@
         <v>1.4598215279168613E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:164" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:164" x14ac:dyDescent="0.25">
       <c r="CB14" s="9" t="s">
         <v>2</v>
       </c>
@@ -5119,7 +5218,7 @@
       <c r="EP14" s="2">
         <v>0</v>
       </c>
-      <c r="EQ14" s="50"/>
+      <c r="EQ14" s="49"/>
       <c r="ER14" s="3">
         <f t="shared" si="1"/>
         <v>199</v>
@@ -5161,7 +5260,7 @@
       <c r="FE14" s="2">
         <v>0</v>
       </c>
-      <c r="FF14" s="50"/>
+      <c r="FF14" s="49"/>
       <c r="FG14" s="3">
         <f t="shared" si="7"/>
         <v>199</v>
@@ -5171,7 +5270,7 @@
         <v>4.4284220130404789E-3</v>
       </c>
     </row>
-    <row r="15" spans="2:164" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:164" x14ac:dyDescent="0.25">
       <c r="CB15" t="s">
         <v>3</v>
       </c>
@@ -5259,7 +5358,7 @@
       <c r="EP15" s="2">
         <v>3.2520325203252001E-2</v>
       </c>
-      <c r="EQ15" s="50"/>
+      <c r="EQ15" s="49"/>
       <c r="ER15" s="3">
         <f t="shared" si="1"/>
         <v>4562</v>
@@ -5301,7 +5400,7 @@
       <c r="FE15" s="2">
         <v>8.7680841736080695E-3</v>
       </c>
-      <c r="FF15" s="50"/>
+      <c r="FF15" s="49"/>
       <c r="FG15" s="3">
         <f t="shared" si="7"/>
         <v>4562</v>
@@ -5311,7 +5410,7 @@
         <v>0.10151990564568174</v>
       </c>
     </row>
-    <row r="16" spans="2:164" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:164" x14ac:dyDescent="0.25">
       <c r="CB16" t="s">
         <v>4</v>
       </c>
@@ -5399,7 +5498,7 @@
       <c r="EP16" s="2">
         <v>8.9430894308943094E-3</v>
       </c>
-      <c r="EQ16" s="50"/>
+      <c r="EQ16" s="49"/>
       <c r="ER16" s="3">
         <f t="shared" si="1"/>
         <v>2480</v>
@@ -5441,7 +5540,7 @@
       <c r="FE16" s="2">
         <v>4.4354838709677403E-3</v>
       </c>
-      <c r="FF16" s="50"/>
+      <c r="FF16" s="49"/>
       <c r="FG16" s="3">
         <f t="shared" si="7"/>
         <v>2480</v>
@@ -5451,7 +5550,7 @@
         <v>5.5188374835881342E-2</v>
       </c>
     </row>
-    <row r="17" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="17" spans="80:164" x14ac:dyDescent="0.25">
       <c r="CB17" t="s">
         <v>5</v>
       </c>
@@ -5541,7 +5640,7 @@
       <c r="EP17" s="2">
         <v>0</v>
       </c>
-      <c r="EQ17" s="50"/>
+      <c r="EQ17" s="49"/>
       <c r="ER17" s="3">
         <f t="shared" si="1"/>
         <v>172</v>
@@ -5583,7 +5682,7 @@
       <c r="FE17" s="2">
         <v>0</v>
       </c>
-      <c r="FF17" s="50"/>
+      <c r="FF17" s="49"/>
       <c r="FG17" s="3">
         <f t="shared" si="7"/>
         <v>172</v>
@@ -5593,7 +5692,7 @@
         <v>3.8275808353917706E-3</v>
       </c>
     </row>
-    <row r="18" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="18" spans="80:164" x14ac:dyDescent="0.25">
       <c r="CB18" s="12" t="s">
         <v>6</v>
       </c>
@@ -5672,7 +5771,7 @@
       <c r="EP18" s="2">
         <v>9.7560975609756097E-3</v>
       </c>
-      <c r="EQ18" s="50"/>
+      <c r="EQ18" s="49"/>
       <c r="ER18" s="3">
         <f t="shared" si="1"/>
         <v>824</v>
@@ -5714,7 +5813,7 @@
       <c r="FE18" s="2">
         <v>1.45631067961165E-2</v>
       </c>
-      <c r="FF18" s="50"/>
+      <c r="FF18" s="49"/>
       <c r="FG18" s="3">
         <f t="shared" si="7"/>
         <v>824</v>
@@ -5724,7 +5823,7 @@
         <v>1.8336782606760575E-2</v>
       </c>
     </row>
-    <row r="19" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="19" spans="80:164" x14ac:dyDescent="0.25">
       <c r="CB19" s="12" t="s">
         <v>12</v>
       </c>
@@ -5811,7 +5910,7 @@
       <c r="EP19" s="2">
         <v>1.6260162601626001E-2</v>
       </c>
-      <c r="EQ19" s="50"/>
+      <c r="EQ19" s="49"/>
       <c r="ER19" s="3">
         <f t="shared" si="1"/>
         <v>1402</v>
@@ -5853,7 +5952,7 @@
       <c r="FE19" s="2">
         <v>1.4265335235378001E-2</v>
       </c>
-      <c r="FF19" s="50"/>
+      <c r="FF19" s="49"/>
       <c r="FG19" s="3">
         <f t="shared" si="7"/>
         <v>1402</v>
@@ -5863,7 +5962,7 @@
         <v>3.1199234483832921E-2</v>
       </c>
     </row>
-    <row r="20" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="20" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX20" s="1" t="s">
         <v>103</v>
       </c>
@@ -5906,7 +6005,7 @@
       <c r="EP20" s="2">
         <v>2.4390243902438998E-3</v>
       </c>
-      <c r="EQ20" s="50"/>
+      <c r="EQ20" s="49"/>
       <c r="ER20" s="3">
         <f t="shared" si="1"/>
         <v>2274</v>
@@ -5948,7 +6047,7 @@
       <c r="FE20" s="2">
         <v>1.31926121372032E-3</v>
       </c>
-      <c r="FF20" s="50"/>
+      <c r="FF20" s="49"/>
       <c r="FG20" s="3">
         <f t="shared" si="7"/>
         <v>2274</v>
@@ -5958,7 +6057,7 @@
         <v>5.0604179184191203E-2</v>
       </c>
     </row>
-    <row r="21" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="21" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX21" s="1" t="s">
         <v>104</v>
       </c>
@@ -6001,7 +6100,7 @@
       <c r="EP21" s="2">
         <v>0.141463414634146</v>
       </c>
-      <c r="EQ21" s="50"/>
+      <c r="EQ21" s="49"/>
       <c r="ER21" s="3">
         <f t="shared" si="1"/>
         <v>5622</v>
@@ -6043,7 +6142,7 @@
       <c r="FE21" s="2">
         <v>3.0949839914621101E-2</v>
       </c>
-      <c r="FF21" s="50"/>
+      <c r="FF21" s="49"/>
       <c r="FG21" s="3">
         <f t="shared" si="7"/>
         <v>5622</v>
@@ -6053,7 +6152,7 @@
         <v>0.12510848521263102</v>
       </c>
     </row>
-    <row r="22" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="22" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX22" s="1" t="s">
         <v>105</v>
       </c>
@@ -6096,7 +6195,7 @@
       <c r="EP22" s="2">
         <v>6.50406504065041E-3</v>
       </c>
-      <c r="EQ22" s="50"/>
+      <c r="EQ22" s="49"/>
       <c r="ER22" s="3">
         <f t="shared" si="1"/>
         <v>606</v>
@@ -6138,7 +6237,7 @@
       <c r="FE22" s="2">
         <v>1.32013201320132E-2</v>
       </c>
-      <c r="FF22" s="50"/>
+      <c r="FF22" s="49"/>
       <c r="FG22" s="3">
         <f t="shared" si="7"/>
         <v>606</v>
@@ -6148,7 +6247,7 @@
         <v>1.3485546431671006E-2</v>
       </c>
     </row>
-    <row r="23" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="23" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX23" s="1" t="s">
         <v>106</v>
       </c>
@@ -6191,7 +6290,7 @@
       <c r="EP23" s="2">
         <v>2.6829268292682899E-2</v>
       </c>
-      <c r="EQ23" s="50"/>
+      <c r="EQ23" s="49"/>
       <c r="ER23" s="3">
         <f t="shared" si="1"/>
         <v>943</v>
@@ -6233,7 +6332,7 @@
       <c r="FE23" s="2">
         <v>3.4994697773064701E-2</v>
       </c>
-      <c r="FF23" s="50"/>
+      <c r="FF23" s="49"/>
       <c r="FG23" s="3">
         <f t="shared" si="7"/>
         <v>943</v>
@@ -6243,7 +6342,7 @@
         <v>2.0984934463804884E-2</v>
       </c>
     </row>
-    <row r="24" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="24" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX24" s="1" t="s">
         <v>107</v>
       </c>
@@ -6286,7 +6385,7 @@
       <c r="EP24" s="2">
         <v>1.05691056910569E-2</v>
       </c>
-      <c r="EQ24" s="50"/>
+      <c r="EQ24" s="49"/>
       <c r="ER24" s="3">
         <f t="shared" si="1"/>
         <v>2141</v>
@@ -6328,7 +6427,7 @@
       <c r="FE24" s="2">
         <v>6.0719290051377897E-3</v>
       </c>
-      <c r="FF24" s="50"/>
+      <c r="FF24" s="49"/>
       <c r="FG24" s="3">
         <f t="shared" si="7"/>
         <v>2141</v>
@@ -6338,7 +6437,7 @@
         <v>4.7644480049847567E-2</v>
       </c>
     </row>
-    <row r="25" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="25" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX25" s="1" t="s">
         <v>108</v>
       </c>
@@ -6381,7 +6480,7 @@
       <c r="EP25" s="2">
         <v>3.2520325203252002E-3</v>
       </c>
-      <c r="EQ25" s="50"/>
+      <c r="EQ25" s="49"/>
       <c r="ER25" s="3">
         <f t="shared" si="1"/>
         <v>1438</v>
@@ -6423,7 +6522,7 @@
       <c r="FE25" s="2">
         <v>2.7816411682892901E-3</v>
       </c>
-      <c r="FF25" s="50"/>
+      <c r="FF25" s="49"/>
       <c r="FG25" s="3">
         <f t="shared" si="7"/>
         <v>1438</v>
@@ -6433,7 +6532,7 @@
         <v>3.2000356054031197E-2</v>
       </c>
     </row>
-    <row r="26" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="26" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX26" s="1" t="s">
         <v>109</v>
       </c>
@@ -6476,7 +6575,7 @@
       <c r="EP26" s="2">
         <v>1.3008130081300801E-2</v>
       </c>
-      <c r="EQ26" s="50"/>
+      <c r="EQ26" s="49"/>
       <c r="ER26" s="3">
         <f t="shared" si="1"/>
         <v>2572</v>
@@ -6518,7 +6617,7 @@
       <c r="FE26" s="2">
         <v>6.2208398133748099E-3</v>
       </c>
-      <c r="FF26" s="50"/>
+      <c r="FF26" s="49"/>
       <c r="FG26" s="3">
         <f t="shared" si="7"/>
         <v>2572</v>
@@ -6528,7 +6627,7 @@
         <v>5.7235685515276941E-2</v>
       </c>
     </row>
-    <row r="27" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="27" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX27" s="1" t="s">
         <v>110</v>
       </c>
@@ -6571,7 +6670,7 @@
       <c r="EP27" s="2">
         <v>9.7560975609756097E-3</v>
       </c>
-      <c r="EQ27" s="50"/>
+      <c r="EQ27" s="49"/>
       <c r="ER27" s="3">
         <f t="shared" si="1"/>
         <v>1472</v>
@@ -6613,7 +6712,7 @@
       <c r="FE27" s="2">
         <v>8.1521739130434798E-3</v>
       </c>
-      <c r="FF27" s="50"/>
+      <c r="FF27" s="49"/>
       <c r="FG27" s="3">
         <f t="shared" si="7"/>
         <v>1472</v>
@@ -6623,7 +6722,7 @@
         <v>3.2756970870329576E-2</v>
       </c>
     </row>
-    <row r="28" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="28" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX28" s="1" t="s">
         <v>111</v>
       </c>
@@ -6666,7 +6765,7 @@
       <c r="EP28" s="2">
         <v>0.18373983739837399</v>
       </c>
-      <c r="EQ28" s="50"/>
+      <c r="EQ28" s="49"/>
       <c r="ER28" s="3">
         <f t="shared" si="1"/>
         <v>2510</v>
@@ -6708,7 +6807,7 @@
       <c r="FE28" s="2">
         <v>9.00398406374502E-2</v>
       </c>
-      <c r="FF28" s="50"/>
+      <c r="FF28" s="49"/>
       <c r="FG28" s="3">
         <f t="shared" si="7"/>
         <v>2510</v>
@@ -6718,7 +6817,7 @@
         <v>5.5855976144379912E-2</v>
       </c>
     </row>
-    <row r="29" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="29" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX29" s="1" t="s">
         <v>112</v>
       </c>
@@ -6761,7 +6860,7 @@
       <c r="EP29" s="2">
         <v>5.3658536585365901E-2</v>
       </c>
-      <c r="EQ29" s="50"/>
+      <c r="EQ29" s="49"/>
       <c r="ER29" s="3">
         <f t="shared" si="1"/>
         <v>1958</v>
@@ -6803,7 +6902,7 @@
       <c r="FE29" s="2">
         <v>3.3707865168539297E-2</v>
       </c>
-      <c r="FF29" s="50"/>
+      <c r="FF29" s="49"/>
       <c r="FG29" s="3">
         <f t="shared" si="7"/>
         <v>1958</v>
@@ -6813,7 +6912,7 @@
         <v>4.3572112068006319E-2</v>
       </c>
     </row>
-    <row r="30" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="30" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX30" s="1" t="s">
         <v>113</v>
       </c>
@@ -6856,7 +6955,7 @@
       <c r="EP30" s="2">
         <v>6.50406504065041E-3</v>
       </c>
-      <c r="EQ30" s="50"/>
+      <c r="EQ30" s="49"/>
       <c r="ER30" s="3">
         <f t="shared" si="1"/>
         <v>1232</v>
@@ -6898,7 +6997,7 @@
       <c r="FE30" s="2">
         <v>6.4935064935064896E-3</v>
       </c>
-      <c r="FF30" s="50"/>
+      <c r="FF30" s="49"/>
       <c r="FG30" s="3">
         <f t="shared" si="7"/>
         <v>1232</v>
@@ -6908,7 +7007,7 @@
         <v>2.7416160402341055E-2</v>
       </c>
     </row>
-    <row r="31" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="31" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX31" s="1" t="s">
         <v>114</v>
       </c>
@@ -6951,7 +7050,7 @@
       <c r="EP31" s="2">
         <v>1.21951219512195E-2</v>
       </c>
-      <c r="EQ31" s="50"/>
+      <c r="EQ31" s="49"/>
       <c r="ER31" s="3">
         <f t="shared" si="1"/>
         <v>301</v>
@@ -6993,7 +7092,7 @@
       <c r="FE31" s="2">
         <v>4.9833887043189397E-2</v>
       </c>
-      <c r="FF31" s="50"/>
+      <c r="FF31" s="49"/>
       <c r="FG31" s="3">
         <f t="shared" si="7"/>
         <v>301</v>
@@ -7003,7 +7102,7 @@
         <v>6.6982664619355987E-3</v>
       </c>
     </row>
-    <row r="32" spans="80:164" x14ac:dyDescent="0.3">
+    <row r="32" spans="80:164" x14ac:dyDescent="0.25">
       <c r="DX32" s="1" t="s">
         <v>115</v>
       </c>
@@ -7046,7 +7145,7 @@
       <c r="EP32" s="2">
         <v>3.2520325203252002E-3</v>
       </c>
-      <c r="EQ32" s="50"/>
+      <c r="EQ32" s="49"/>
       <c r="ER32" s="3">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -7088,7 +7187,7 @@
       <c r="FE32" s="2">
         <v>3.1007751937984499E-2</v>
       </c>
-      <c r="FF32" s="50"/>
+      <c r="FF32" s="49"/>
       <c r="FG32" s="3">
         <f t="shared" si="7"/>
         <v>129</v>
@@ -7098,7 +7197,7 @@
         <v>2.8706856265438281E-3</v>
       </c>
     </row>
-    <row r="33" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="33" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX33" s="1" t="s">
         <v>116</v>
       </c>
@@ -7141,7 +7240,7 @@
       <c r="EP33" s="2">
         <v>0.104065040650407</v>
       </c>
-      <c r="EQ33" s="50"/>
+      <c r="EQ33" s="49"/>
       <c r="ER33" s="3">
         <f t="shared" si="1"/>
         <v>2370</v>
@@ -7183,7 +7282,7 @@
       <c r="FE33" s="2">
         <v>5.4008438818565402E-2</v>
       </c>
-      <c r="FF33" s="50"/>
+      <c r="FF33" s="49"/>
       <c r="FG33" s="3">
         <f t="shared" si="7"/>
         <v>2370</v>
@@ -7193,7 +7292,7 @@
         <v>5.274050337138661E-2</v>
       </c>
     </row>
-    <row r="34" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="34" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX34" s="1" t="s">
         <v>117</v>
       </c>
@@ -7236,7 +7335,7 @@
       <c r="EP34" s="2">
         <v>0.16585365853658501</v>
       </c>
-      <c r="EQ34" s="50"/>
+      <c r="EQ34" s="49"/>
       <c r="ER34" s="3">
         <f t="shared" si="1"/>
         <v>1727</v>
@@ -7278,7 +7377,7 @@
       <c r="FE34" s="2">
         <v>0.11812391430225801</v>
       </c>
-      <c r="FF34" s="50"/>
+      <c r="FF34" s="49"/>
       <c r="FG34" s="3">
         <f t="shared" si="7"/>
         <v>1727</v>
@@ -7288,7 +7387,7 @@
         <v>3.8431581992567375E-2</v>
       </c>
     </row>
-    <row r="35" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="35" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX35" s="1" t="s">
         <v>118</v>
       </c>
@@ -7331,7 +7430,7 @@
       <c r="EP35" s="2">
         <v>1.6260162601626001E-3</v>
       </c>
-      <c r="EQ35" s="50"/>
+      <c r="EQ35" s="49"/>
       <c r="ER35" s="3">
         <f t="shared" si="1"/>
         <v>711</v>
@@ -7373,7 +7472,7 @@
       <c r="FE35" s="2">
         <v>2.81293952180028E-3</v>
       </c>
-      <c r="FF35" s="50"/>
+      <c r="FF35" s="49"/>
       <c r="FG35" s="3">
         <f t="shared" si="7"/>
         <v>711</v>
@@ -7383,7 +7482,7 @@
         <v>1.5822151011415982E-2</v>
       </c>
     </row>
-    <row r="36" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="36" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX36" s="1" t="s">
         <v>119</v>
       </c>
@@ -7426,7 +7525,7 @@
       <c r="EP36" s="2">
         <v>0.18292682926829301</v>
       </c>
-      <c r="EQ36" s="50"/>
+      <c r="EQ36" s="49"/>
       <c r="ER36" s="3">
         <f t="shared" si="1"/>
         <v>4970</v>
@@ -7468,7 +7567,7 @@
       <c r="FE36" s="2">
         <v>4.5271629778672003E-2</v>
       </c>
-      <c r="FF36" s="50"/>
+      <c r="FF36" s="49"/>
       <c r="FG36" s="3">
         <f t="shared" si="7"/>
         <v>4970</v>
@@ -7478,7 +7577,7 @@
         <v>0.11059928344126221</v>
       </c>
     </row>
-    <row r="37" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="37" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX37" s="1" t="s">
         <v>120</v>
       </c>
@@ -7521,7 +7620,7 @@
       <c r="EP37" s="24">
         <v>2.4390243902438998E-3</v>
       </c>
-      <c r="EQ37" s="51"/>
+      <c r="EQ37" s="50"/>
       <c r="ER37" s="3">
         <f t="shared" si="1"/>
         <v>444</v>
@@ -7563,7 +7662,7 @@
       <c r="FE37" s="24">
         <v>6.7567567567567597E-3</v>
       </c>
-      <c r="FF37" s="51"/>
+      <c r="FF37" s="50"/>
       <c r="FG37" s="3">
         <f t="shared" si="7"/>
         <v>444</v>
@@ -7573,7 +7672,7 @@
         <v>9.8804993657787572E-3</v>
       </c>
     </row>
-    <row r="38" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="38" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX38" s="1" t="s">
         <v>121</v>
       </c>
@@ -7673,7 +7772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="39" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX39" s="1" t="s">
         <v>122</v>
       </c>
@@ -7684,7 +7783,7 @@
         <v>5.2940783763936197E-2</v>
       </c>
     </row>
-    <row r="40" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="40" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX40" s="1" t="s">
         <v>123</v>
       </c>
@@ -7695,7 +7794,7 @@
         <v>4.7822507065447203E-2</v>
       </c>
     </row>
-    <row r="41" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="41" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX41" s="1" t="s">
         <v>124</v>
       </c>
@@ -7706,7 +7805,7 @@
         <v>4.4106193114805202E-2</v>
       </c>
     </row>
-    <row r="42" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="42" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX42" s="1" t="s">
         <v>125</v>
       </c>
@@ -7717,7 +7816,7 @@
         <v>3.7719473930168897E-2</v>
       </c>
     </row>
-    <row r="43" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="43" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX43" s="1" t="s">
         <v>126</v>
       </c>
@@ -7728,7 +7827,7 @@
         <v>3.29127445089792E-2</v>
       </c>
     </row>
-    <row r="44" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="44" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX44" s="1" t="s">
         <v>127</v>
       </c>
@@ -7739,7 +7838,7 @@
         <v>2.7749961056590298E-2</v>
       </c>
     </row>
-    <row r="45" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="45" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX45" s="1" t="s">
         <v>128</v>
       </c>
@@ -7750,7 +7849,7 @@
         <v>2.2475910719451701E-2</v>
       </c>
     </row>
-    <row r="46" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="46" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX46" s="1" t="s">
         <v>129</v>
       </c>
@@ -7761,7 +7860,7 @@
         <v>1.9471704831208098E-2</v>
       </c>
     </row>
-    <row r="47" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="47" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX47" s="1" t="s">
         <v>130</v>
       </c>
@@ -7772,7 +7871,7 @@
         <v>1.5288069964617099E-2</v>
       </c>
     </row>
-    <row r="48" spans="128:164" x14ac:dyDescent="0.3">
+    <row r="48" spans="128:164" x14ac:dyDescent="0.25">
       <c r="DX48" s="1" t="s">
         <v>131</v>
       </c>
@@ -7783,7 +7882,7 @@
         <v>1.17497830295747E-2</v>
       </c>
     </row>
-    <row r="49" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="49" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX49" s="1" t="s">
         <v>132</v>
       </c>
@@ -7794,7 +7893,7 @@
         <v>8.0557224558826801E-3</v>
       </c>
     </row>
-    <row r="50" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="50" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX50" s="1" t="s">
         <v>133</v>
       </c>
@@ -7805,7 +7904,7 @@
         <v>6.5869995771858404E-3</v>
       </c>
     </row>
-    <row r="51" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="51" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX51" s="1" t="s">
         <v>134</v>
       </c>
@@ -7816,7 +7915,7 @@
         <v>4.2058882435409596E-3</v>
       </c>
     </row>
-    <row r="52" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="52" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX52" s="1" t="s">
         <v>135</v>
       </c>
@@ -7827,7 +7926,7 @@
         <v>3.2934997885929202E-3</v>
       </c>
     </row>
-    <row r="53" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="53" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX53" s="1" t="s">
         <v>136</v>
       </c>
@@ -7838,7 +7937,7 @@
         <v>2.2253376949952202E-3</v>
       </c>
     </row>
-    <row r="54" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="54" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX54" s="1" t="s">
         <v>137</v>
       </c>
@@ -7849,7 +7948,7 @@
         <v>1.4019627478469899E-3</v>
       </c>
     </row>
-    <row r="55" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="55" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX55" s="1" t="s">
         <v>138</v>
       </c>
@@ -7860,7 +7959,7 @@
         <v>6.8985468544851701E-4</v>
       </c>
     </row>
-    <row r="56" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="56" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX56" s="1" t="s">
         <v>139</v>
       </c>
@@ -7871,7 +7970,7 @@
         <v>3.1154727729933E-4</v>
       </c>
     </row>
-    <row r="57" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="57" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX57" s="1" t="s">
         <v>140</v>
       </c>
@@ -7882,7 +7981,7 @@
         <v>2.00280392549569E-4</v>
       </c>
     </row>
-    <row r="58" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="58" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX58" s="1" t="s">
         <v>141</v>
       </c>
@@ -7893,7 +7992,7 @@
         <v>1.3352026169971299E-4</v>
       </c>
     </row>
-    <row r="59" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="59" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX59" s="1" t="s">
         <v>142</v>
       </c>
@@ -7904,7 +8003,7 @@
         <v>1.7802701559961701E-4</v>
       </c>
     </row>
-    <row r="60" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="60" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX60" s="1" t="s">
         <v>143</v>
       </c>
@@ -7915,7 +8014,7 @@
         <v>4.45067538999043E-5</v>
       </c>
     </row>
-    <row r="61" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="61" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX61" s="1" t="s">
         <v>144</v>
       </c>
@@ -7926,7 +8025,7 @@
         <v>2.2253376949952201E-5</v>
       </c>
     </row>
-    <row r="62" spans="128:130" x14ac:dyDescent="0.3">
+    <row r="62" spans="128:130" x14ac:dyDescent="0.25">
       <c r="DX62" s="1" t="s">
         <v>186</v>
       </c>
@@ -7939,25 +8038,55 @@
     </row>
   </sheetData>
   <mergeCells count="85">
-    <mergeCell ref="FF5:FF9"/>
-    <mergeCell ref="FF11:FF37"/>
-    <mergeCell ref="EU1:FH2"/>
-    <mergeCell ref="EU3:EU4"/>
-    <mergeCell ref="EV3:EW3"/>
-    <mergeCell ref="EX3:EY3"/>
-    <mergeCell ref="EZ3:FA3"/>
-    <mergeCell ref="FB3:FC3"/>
-    <mergeCell ref="FD3:FE3"/>
-    <mergeCell ref="FF3:FF4"/>
-    <mergeCell ref="FG3:FH3"/>
-    <mergeCell ref="BB5:BB9"/>
-    <mergeCell ref="CV1:CX2"/>
-    <mergeCell ref="BX1:BZ2"/>
-    <mergeCell ref="CF1:CH2"/>
-    <mergeCell ref="CB1:CD2"/>
-    <mergeCell ref="CN1:CP2"/>
-    <mergeCell ref="CJ1:CL2"/>
-    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DD11:DF12"/>
+    <mergeCell ref="ER3:ES3"/>
+    <mergeCell ref="EF1:ES2"/>
+    <mergeCell ref="CB11:CD12"/>
+    <mergeCell ref="CZ11:DB12"/>
+    <mergeCell ref="DL8:DN9"/>
+    <mergeCell ref="EQ11:EQ37"/>
+    <mergeCell ref="DX1:DZ2"/>
+    <mergeCell ref="DT1:DV2"/>
+    <mergeCell ref="EQ3:EQ4"/>
+    <mergeCell ref="EF3:EF4"/>
+    <mergeCell ref="EB1:ED2"/>
+    <mergeCell ref="EQ5:EQ9"/>
+    <mergeCell ref="EG3:EH3"/>
+    <mergeCell ref="EI3:EJ3"/>
+    <mergeCell ref="EK3:EL3"/>
+    <mergeCell ref="EM3:EN3"/>
+    <mergeCell ref="EO3:EP3"/>
+    <mergeCell ref="DL1:DN2"/>
+    <mergeCell ref="DP1:DR2"/>
+    <mergeCell ref="AF5:AF9"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BT5:BT9"/>
+    <mergeCell ref="AF1:AY2"/>
+    <mergeCell ref="CR1:CT2"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="AX5:AX9"/>
+    <mergeCell ref="BB1:BU2"/>
+    <mergeCell ref="BB3:BC4"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="AF3:AG4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="CZ1:DB2"/>
+    <mergeCell ref="DD1:DF2"/>
+    <mergeCell ref="DH1:DJ2"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AX3:AX4"/>
+    <mergeCell ref="AY3:AY4"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="BT3:BT4"/>
+    <mergeCell ref="BU3:BU4"/>
+    <mergeCell ref="BF3:BG3"/>
     <mergeCell ref="AB1:AD2"/>
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="T5:T9"/>
@@ -7974,56 +8103,26 @@
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="B3:C4"/>
     <mergeCell ref="U3:U4"/>
+    <mergeCell ref="BB5:BB9"/>
+    <mergeCell ref="CV1:CX2"/>
+    <mergeCell ref="BX1:BZ2"/>
+    <mergeCell ref="CF1:CH2"/>
+    <mergeCell ref="CB1:CD2"/>
+    <mergeCell ref="CN1:CP2"/>
+    <mergeCell ref="CJ1:CL2"/>
+    <mergeCell ref="BR3:BS3"/>
     <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="CZ1:DB2"/>
-    <mergeCell ref="DD1:DF2"/>
-    <mergeCell ref="DH1:DJ2"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AX3:AX4"/>
-    <mergeCell ref="AY3:AY4"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="BT3:BT4"/>
-    <mergeCell ref="BU3:BU4"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="AF3:AG4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="EM3:EN3"/>
-    <mergeCell ref="EO3:EP3"/>
-    <mergeCell ref="DL1:DN2"/>
-    <mergeCell ref="DP1:DR2"/>
-    <mergeCell ref="AF5:AF9"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BT5:BT9"/>
-    <mergeCell ref="AF1:AY2"/>
-    <mergeCell ref="CR1:CT2"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="AX5:AX9"/>
-    <mergeCell ref="BB1:BU2"/>
-    <mergeCell ref="BB3:BC4"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="DD11:DF12"/>
-    <mergeCell ref="ER3:ES3"/>
-    <mergeCell ref="EF1:ES2"/>
-    <mergeCell ref="CB11:CD12"/>
-    <mergeCell ref="CZ11:DB12"/>
-    <mergeCell ref="DL8:DN9"/>
-    <mergeCell ref="EQ11:EQ37"/>
-    <mergeCell ref="DX1:DZ2"/>
-    <mergeCell ref="DT1:DV2"/>
-    <mergeCell ref="EQ3:EQ4"/>
-    <mergeCell ref="EF3:EF4"/>
-    <mergeCell ref="EB1:ED2"/>
-    <mergeCell ref="EQ5:EQ9"/>
-    <mergeCell ref="EG3:EH3"/>
-    <mergeCell ref="EI3:EJ3"/>
-    <mergeCell ref="EK3:EL3"/>
+    <mergeCell ref="FF5:FF9"/>
+    <mergeCell ref="FF11:FF37"/>
+    <mergeCell ref="EU1:FH2"/>
+    <mergeCell ref="EU3:EU4"/>
+    <mergeCell ref="EV3:EW3"/>
+    <mergeCell ref="EX3:EY3"/>
+    <mergeCell ref="EZ3:FA3"/>
+    <mergeCell ref="FB3:FC3"/>
+    <mergeCell ref="FD3:FE3"/>
+    <mergeCell ref="FF3:FF4"/>
+    <mergeCell ref="FG3:FH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
